--- a/From_wincc/Symap_1.xlsx
+++ b/From_wincc/Symap_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk2\РЗА\!работа с tiaportal\!!tia 15_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CF54DD-175B-4A18-8285-6170156AFA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEF8E8E-930D-4E2E-BDA7-82E7FA0FA0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2801,9 +2801,10 @@
   <dimension ref="A1:AC254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="1" max="1" width="95.7109375" customWidth="1"/>
     <col min="2" max="2" width="39.85546875" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
